--- a/Result/profitability/4129.xlsx
+++ b/Result/profitability/4129.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>1.095</v>
       </c>
       <c r="N2" t="n">
-        <v>75.13749999999999</v>
+        <v>75.01375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8375</v>
+        <v>0.85875</v>
       </c>
       <c r="N3" t="n">
-        <v>72.09625</v>
+        <v>72.3275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>69.03375</v>
+        <v>68.76375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.295</v>
+        <v>0.415</v>
       </c>
       <c r="N5" t="n">
-        <v>65.0425</v>
+        <v>65.3425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28</v>
+        <v>0.20875</v>
       </c>
       <c r="N6" t="n">
-        <v>62.1125</v>
+        <v>62.43875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07750000000000003</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>59.70625</v>
+        <v>59.67</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05374999999999999</v>
+        <v>0.01249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>57.5125</v>
+        <v>57.37375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.27</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04125</v>
+        <v>-0.04125000000000002</v>
       </c>
       <c r="N10" t="n">
         <v>57.00375</v>
@@ -1772,7 +1772,7 @@
         <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05375</v>
+        <v>0.05374999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>57.04</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D75" t="n">
+        <v>337</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1228</v>
+      </c>
+      <c r="F75" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="G75" t="n">
+        <v>188</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>182</v>
+      </c>
+      <c r="K75" t="n">
+        <v>139</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.36125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>78.19125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5824175824175823</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.109999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01394647568790053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03154574132492116</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
